--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T07:37:23+00:00</t>
+    <t>2024-10-25T08:22:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:22:33+00:00</t>
+    <t>2024-10-28T11:11:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:11:19+00:00</t>
+    <t>2024-10-28T11:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T11:26:59+00:00</t>
+    <t>2024-10-29T09:20:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:20:35+00:00</t>
+    <t>2024-10-31T11:17:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T11:17:53+00:00</t>
+    <t>2024-10-31T15:29:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T15:29:56+00:00</t>
+    <t>2024-11-05T14:48:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:48:02+00:00</t>
+    <t>2024-11-07T21:06:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:06:19+00:00</t>
+    <t>2024-11-07T21:57:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-07T21:57:27+00:00</t>
+    <t>2024-11-07T22:09:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-09T09:07:40+00:00</t>
+    <t>2024-11-11T13:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:26:20+00:00</t>
+    <t>2024-11-12T06:42:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:42:28+00:00</t>
+    <t>2024-11-12T07:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:20:07+00:00</t>
+    <t>2024-11-12T07:35:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:35:41+00:00</t>
+    <t>2024-11-12T07:42:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T07:42:03+00:00</t>
+    <t>2024-11-12T08:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:38:00+00:00</t>
+    <t>2024-11-12T08:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3215" uniqueCount="534">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:47:06+00:00</t>
+    <t>2024-11-12T20:06:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1253,6 +1253,48 @@
     <t>https://termgit.elga.gv.at/CodeSystem/bmg-icd-10-2024</t>
   </si>
   <si>
+    <t>Condition.code.coding:ICD10.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.system</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.system</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.version</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.version</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.display</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.display</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:ICD10.userSelected</t>
+  </si>
+  <si>
+    <t>Condition.code.coding.userSelected</t>
+  </si>
+  <si>
     <t>Condition.code.coding:HDG</t>
   </si>
   <si>
@@ -1260,6 +1302,30 @@
   </si>
   <si>
     <t>http://example.org/ValueSet/moped-LKFHauptdiagnosegruppen-valueset</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.id</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.extension</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.system</t>
+  </si>
+  <si>
+    <t>http://tbd.at/MOPED-LKFHauptdiagnosegruppen</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.version</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.code</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.display</t>
+  </si>
+  <si>
+    <t>Condition.code.coding:HDG.userSelected</t>
   </si>
   <si>
     <t>Condition.code.text</t>
@@ -1911,7 +1977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO72"/>
+  <dimension ref="A1:AO86"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="66.84765625" customWidth="true" bestFit="true"/>
@@ -7700,17 +7766,15 @@
         <v>397</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="C50" t="s" s="2">
         <v>398</v>
       </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>88</v>
@@ -7722,23 +7786,19 @@
         <v>19</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>199</v>
+        <v>90</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>200</v>
+        <v>162</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>203</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>19</v>
       </c>
@@ -7762,11 +7822,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>399</v>
+        <v>19</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7784,19 +7846,19 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>204</v>
+        <v>164</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>19</v>
@@ -7805,10 +7867,10 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>205</v>
+        <v>19</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>206</v>
+        <v>166</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>19</v>
@@ -7816,21 +7878,21 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>400</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>19</v>
@@ -7839,23 +7901,21 @@
         <v>19</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>259</v>
+        <v>137</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>260</v>
+        <v>169</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>262</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>19</v>
       </c>
@@ -7891,31 +7951,31 @@
         <v>19</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>19</v>
@@ -7924,10 +7984,10 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>265</v>
+        <v>166</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>19</v>
@@ -7938,7 +7998,7 @@
         <v>401</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7946,10 +8006,10 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>19</v>
@@ -7961,18 +8021,20 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>185</v>
+        <v>102</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>402</v>
+        <v>213</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>403</v>
+        <v>214</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
       </c>
@@ -7981,7 +8043,7 @@
         <v>19</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>19</v>
+        <v>396</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>19</v>
@@ -7996,13 +8058,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>405</v>
+        <v>19</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8020,13 +8082,13 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>401</v>
+        <v>217</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>19</v>
@@ -8038,32 +8100,32 @@
         <v>19</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>407</v>
+        <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>408</v>
+        <v>219</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>409</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>411</v>
+        <v>19</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>88</v>
@@ -8078,18 +8140,18 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>412</v>
+        <v>222</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>413</v>
+        <v>223</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>415</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>19</v>
       </c>
@@ -8137,10 +8199,10 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>226</v>
       </c>
       <c r="AG53" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH53" t="s" s="2">
         <v>88</v>
@@ -8152,16 +8214,16 @@
         <v>100</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>416</v>
+        <v>19</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>417</v>
+        <v>227</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>418</v>
+        <v>228</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>19</v>
@@ -8169,10 +8231,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>419</v>
+        <v>405</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8180,7 +8242,7 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>88</v>
@@ -8195,18 +8257,18 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>420</v>
+        <v>108</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>421</v>
+        <v>231</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
       </c>
@@ -8254,7 +8316,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>419</v>
+        <v>235</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8263,22 +8325,22 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>424</v>
+        <v>19</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>425</v>
+        <v>237</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>426</v>
+        <v>238</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>19</v>
@@ -8286,10 +8348,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>427</v>
+        <v>408</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8312,18 +8374,18 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>428</v>
+        <v>222</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>429</v>
+        <v>241</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
       </c>
@@ -8371,7 +8433,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>427</v>
+        <v>244</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8380,22 +8442,22 @@
         <v>88</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>432</v>
+        <v>19</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>433</v>
+        <v>245</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>434</v>
+        <v>246</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>19</v>
@@ -8403,10 +8465,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>435</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>410</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8426,21 +8488,23 @@
         <v>19</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>428</v>
+        <v>249</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>436</v>
+        <v>250</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>437</v>
+        <v>251</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
       </c>
@@ -8488,7 +8552,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>435</v>
+        <v>254</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8497,22 +8561,22 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>439</v>
+        <v>19</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>440</v>
+        <v>19</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>441</v>
+        <v>256</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>19</v>
@@ -8520,18 +8584,20 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>442</v>
+        <v>411</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C57" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="C57" t="s" s="2">
+        <v>412</v>
+      </c>
       <c r="D57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>88</v>
@@ -8546,18 +8612,20 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>443</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>444</v>
+        <v>200</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>445</v>
+        <v>201</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>202</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>203</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>19</v>
       </c>
@@ -8581,13 +8649,11 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>19</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>19</v>
+        <v>413</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -8605,13 +8671,13 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>442</v>
+        <v>204</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>19</v>
@@ -8620,16 +8686,16 @@
         <v>100</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>447</v>
+        <v>19</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>448</v>
+        <v>205</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>449</v>
+        <v>206</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>19</v>
@@ -8637,10 +8703,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>450</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>450</v>
+        <v>398</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8651,7 +8717,7 @@
         <v>77</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>19</v>
@@ -8660,16 +8726,16 @@
         <v>19</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>451</v>
+        <v>90</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>452</v>
+        <v>162</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>453</v>
+        <v>163</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8720,19 +8786,19 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>450</v>
+        <v>164</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>19</v>
+        <v>165</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>100</v>
+        <v>19</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>19</v>
@@ -8744,7 +8810,7 @@
         <v>19</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>454</v>
+        <v>166</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>19</v>
@@ -8752,21 +8818,21 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>455</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>19</v>
+        <v>135</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>19</v>
@@ -8778,15 +8844,17 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>162</v>
+        <v>137</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -8823,31 +8891,31 @@
         <v>19</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>19</v>
+        <v>171</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>19</v>
+        <v>141</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>19</v>
@@ -8867,21 +8935,21 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>416</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>19</v>
@@ -8890,21 +8958,23 @@
         <v>19</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>136</v>
+        <v>102</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>137</v>
+        <v>213</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>169</v>
+        <v>214</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
       </c>
@@ -8913,7 +8983,7 @@
         <v>19</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>19</v>
+        <v>417</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>19</v>
@@ -8952,19 +9022,19 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>172</v>
+        <v>217</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>19</v>
@@ -8973,10 +9043,10 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>19</v>
+        <v>218</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>19</v>
@@ -8984,46 +9054,44 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>457</v>
+        <v>418</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>457</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>458</v>
+        <v>19</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="J61" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>136</v>
+        <v>222</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>459</v>
+        <v>223</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>460</v>
+        <v>224</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>19</v>
       </c>
@@ -9071,19 +9139,19 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>461</v>
+        <v>226</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>19</v>
@@ -9092,10 +9160,10 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>19</v>
+        <v>227</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>133</v>
+        <v>228</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>19</v>
@@ -9103,10 +9171,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>462</v>
+        <v>419</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>462</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9129,16 +9197,18 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>185</v>
+        <v>108</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>463</v>
+        <v>231</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>464</v>
+        <v>232</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
       </c>
@@ -9162,11 +9232,13 @@
         <v>19</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>466</v>
+        <v>19</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>19</v>
@@ -9184,7 +9256,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>462</v>
+        <v>235</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9193,7 +9265,7 @@
         <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>100</v>
@@ -9205,10 +9277,10 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>19</v>
+        <v>237</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>467</v>
+        <v>238</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>19</v>
@@ -9216,10 +9288,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>468</v>
+        <v>420</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>468</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9227,7 +9299,7 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>88</v>
@@ -9242,16 +9314,18 @@
         <v>89</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>469</v>
+        <v>222</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>470</v>
+        <v>241</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>471</v>
+        <v>242</v>
       </c>
       <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+      <c r="O63" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
       </c>
@@ -9299,31 +9373,31 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>468</v>
+        <v>244</v>
       </c>
       <c r="AG63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AH63" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>19</v>
+        <v>236</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>472</v>
+        <v>19</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>19</v>
+        <v>245</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>473</v>
+        <v>246</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>19</v>
@@ -9331,10 +9405,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>474</v>
+        <v>421</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>410</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9345,7 +9419,7 @@
         <v>77</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>19</v>
@@ -9354,19 +9428,23 @@
         <v>19</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>451</v>
+        <v>249</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>475</v>
+        <v>250</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
       </c>
@@ -9414,19 +9492,19 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>474</v>
+        <v>254</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>477</v>
+        <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>19</v>
@@ -9435,10 +9513,10 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>19</v>
+        <v>255</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>478</v>
+        <v>256</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>19</v>
@@ -9446,10 +9524,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>422</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>422</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9469,19 +9547,23 @@
         <v>19</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
         <v>222</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>162</v>
+        <v>259</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>262</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
       </c>
@@ -9529,7 +9611,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>164</v>
+        <v>263</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9538,10 +9620,10 @@
         <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>165</v>
+        <v>19</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>19</v>
@@ -9550,10 +9632,10 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>19</v>
+        <v>264</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>166</v>
+        <v>265</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>19</v>
@@ -9561,14 +9643,14 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>480</v>
+        <v>423</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9584,19 +9666,19 @@
         <v>19</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>136</v>
+        <v>185</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>137</v>
+        <v>424</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>169</v>
+        <v>425</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>139</v>
+        <v>426</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9622,13 +9704,13 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>19</v>
+        <v>381</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>19</v>
+        <v>427</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>19</v>
+        <v>428</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -9646,7 +9728,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>423</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9658,65 +9740,63 @@
         <v>19</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>19</v>
+        <v>429</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>166</v>
+        <v>430</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>19</v>
+        <v>431</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>481</v>
+        <v>432</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>458</v>
+        <v>433</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>89</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>136</v>
+        <v>434</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>436</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>145</v>
+        <v>437</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -9765,31 +9845,31 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>19</v>
+        <v>438</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>19</v>
+        <v>439</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>133</v>
+        <v>440</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>19</v>
@@ -9797,10 +9877,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9808,7 +9888,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>88</v>
@@ -9820,18 +9900,20 @@
         <v>19</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>185</v>
+        <v>442</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>483</v>
+        <v>443</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9856,13 +9938,13 @@
         <v>19</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>484</v>
+        <v>19</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>485</v>
+        <v>19</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>19</v>
@@ -9880,7 +9962,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>482</v>
+        <v>441</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9889,22 +9971,22 @@
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>486</v>
+        <v>19</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>19</v>
+        <v>446</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>487</v>
+        <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>312</v>
+        <v>447</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>387</v>
+        <v>448</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>19</v>
@@ -9912,10 +9994,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9926,7 +10008,7 @@
         <v>77</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>19</v>
@@ -9935,18 +10017,20 @@
         <v>19</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>489</v>
+        <v>450</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>490</v>
+        <v>451</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>452</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>453</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -9995,31 +10079,31 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>488</v>
+        <v>449</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>486</v>
+        <v>19</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>19</v>
+        <v>454</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>19</v>
+        <v>455</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>492</v>
+        <v>456</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>19</v>
@@ -10027,10 +10111,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10053,15 +10137,17 @@
         <v>19</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>185</v>
+        <v>450</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>494</v>
+        <v>458</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10086,13 +10172,13 @@
         <v>19</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>381</v>
+        <v>19</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>496</v>
+        <v>19</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>497</v>
+        <v>19</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -10110,7 +10196,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>493</v>
+        <v>457</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10119,13 +10205,13 @@
         <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>19</v>
+        <v>461</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>19</v>
+        <v>462</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>19</v>
@@ -10134,7 +10220,7 @@
         <v>19</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>498</v>
+        <v>463</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>19</v>
@@ -10142,10 +10228,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10156,7 +10242,7 @@
         <v>77</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>19</v>
@@ -10168,16 +10254,16 @@
         <v>89</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>500</v>
+        <v>465</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>468</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10203,11 +10289,13 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="Y71" s="2"/>
+        <v>19</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>19</v>
+      </c>
       <c r="Z71" t="s" s="2">
-        <v>504</v>
+        <v>19</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -10225,13 +10313,13 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>19</v>
@@ -10240,16 +10328,16 @@
         <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>19</v>
+        <v>469</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>19</v>
+        <v>470</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>19</v>
@@ -10257,10 +10345,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10280,16 +10368,16 @@
         <v>19</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>19</v>
+        <v>89</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>507</v>
+        <v>473</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>508</v>
+        <v>474</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>509</v>
+        <v>475</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10340,7 +10428,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>506</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10361,12 +10449,1632 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="Y76" s="2"/>
+      <c r="Z76" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="P81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="B83" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K83" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="AO72" t="s" s="2">
+      <c r="L83" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="Y85" s="2"/>
+      <c r="Z85" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AO86" t="s" s="2">
         <v>19</v>
       </c>
     </row>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T20:06:39+00:00</t>
+    <t>2024-11-14T06:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T06:51:52+00:00</t>
+    <t>2024-11-14T14:31:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:31:22+00:00</t>
+    <t>2024-11-14T14:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:34:15+00:00</t>
+    <t>2024-11-14T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:43:46+00:00</t>
+    <t>2024-11-15T18:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T18:55:56+00:00</t>
+    <t>2024-11-15T19:04:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:04:50+00:00</t>
+    <t>2024-11-15T19:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:21:45+00:00</t>
+    <t>2024-11-15T20:14:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:14:47+00:00</t>
+    <t>2024-11-17T19:44:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:44:33+00:00</t>
+    <t>2024-11-19T10:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
+++ b/r5-ELGA-MOPED-POC-IG/StructureDefinition-MOPEDCondition.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T10:30:26+00:00</t>
+    <t>2025-02-10T09:28:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
